--- a/5. Other/Đề xuất mua hàng/Năm 2026/Đề Xuất Mua Vật Tư Sản Xuất TG102LE4G(0056) Lô 1_2026.xlsx
+++ b/5. Other/Đề xuất mua hàng/Năm 2026/Đề Xuất Mua Vật Tư Sản Xuất TG102LE4G(0056) Lô 1_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Đề xuất mua hàng\Năm 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6DE3AC-0398-4762-B442-3CA6BC66190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88094889-E511-4F3B-96E5-021B6131A38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,43 +279,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,98 +666,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13" t="s">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="14"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="14"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="9"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18" t="s">
+      <c r="G5" s="21"/>
+      <c r="H5" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="18"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4"/>
@@ -777,8 +777,8 @@
       <c r="A8" s="3">
         <v>2</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
@@ -814,40 +814,40 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="14"/>
     </row>
     <row r="12" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
@@ -890,22 +890,22 @@
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11" t="s">
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -929,24 +929,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A11:B11"/>
@@ -959,6 +941,24 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
